--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_spine_animation_state[骨骼动画枚举_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_spine_animation_state[骨骼动画枚举_FrameWork].xlsx
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>idle,wait,idle1,wait1</t>
+          <t>idle,wait,idle1,wait1,stand</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_spine_animation_state[骨骼动画枚举_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_spine_animation_state[骨骼动画枚举_FrameWork].xlsx
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>walk,walk1,move</t>
+          <t>walk,walk1,move,move1,move2</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
